--- a/pensum/ma06/LOM_Ovingsark_Markedsforing_kap06_Produktbidrag_og_sortiment_NY.xlsx
+++ b/pensum/ma06/LOM_Ovingsark_Markedsforing_kap06_Produktbidrag_og_sortiment_NY.xlsx
@@ -276,7 +276,7 @@
     <t xml:space="preserve">Hjertnes, Frode: Markedsføring, organisasjon og ledelse for LØM-emnet, 4. utgave, kapittel 6 «Produkt som konkurransevirkemiddel», avsnitt 6.1 til 6.9.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dekningsbidrag, montørtimer og kostsats: Bok 1 kapittel 2 og 5. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+    <t xml:space="preserve">Dekningsbidrag, montørtimer og kostsats: Økonomistyring for LØM-emnet, kapittel 2 og 5. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av begge bøkene.</t>
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Seks tjenestegrupper. Endre de gule cellene — alt annet regner seg selv.</t>
   </si>
   <si>
-    <t xml:space="preserve">Salgsinntekt 2026 (Bok 1 kap. 3)</t>
+    <t xml:space="preserve">Salgsinntekt 2026 (Økonomistyring for LØM-emnet kap. 3)</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys Elektro AS sin egen omsetning. Gruppene deler denne summen.</t>
@@ -426,7 +426,7 @@
     <t xml:space="preserve">Kostsats per montørtime</t>
   </si>
   <si>
-    <t xml:space="preserve">Dekningsbidrag 2026, hele bedriften (Bok 1 kap. 2)</t>
+    <t xml:space="preserve">Dekningsbidrag 2026, hele bedriften (Økonomistyring for LØM-emnet kap. 2)</t>
   </si>
   <si>
     <t xml:space="preserve">Fakturerte montørtimer 2026</t>
@@ -543,7 +543,7 @@
     <t xml:space="preserve">Prøv dette: sett montørtimene på nybygg i E13 ned med to. Se hva som skjer med DB per montørtime — og hvor lite som skal til før den svakeste tjenesten er en av de beste.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes kap. 6 om produktnivåer, kvalitet og sortiment. Dekningsbidrag og montørtimer: Bok 1 kap. 2 og 5. Prisene på typeoppdragene er Nordlys Elektro AS sine egne.</t>
+    <t xml:space="preserve">Kilde: Hjertnes kap. 6 om produktnivåer, kvalitet og sortiment. Dekningsbidrag og montørtimer: Økonomistyring for LØM-emnet kap. 2 og 5. Prisene på typeoppdragene er Nordlys Elektro AS sine egne.</t>
   </si>
   <si>
     <t xml:space="preserve">Tre scenarioer</t>
@@ -714,7 +714,7 @@
     <t xml:space="preserve">Her SKAL det stå OK med tallene som ligger inne. Et anslag som gir bedre bidrag enn alt annet fra dag én, er nesten alltid for optimistisk.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes kap. 6.6 om produktutvikling, 6.7 om livssyklusen og 6.8 om produktsanering. Dekningsbidrag per montørtime: Bok 1 kap. 2. Markedstall: NVE, «Solkraft», nve.no/energi/energisystem/solkraft (tall per 31.12.2024, hentet 09.09.2026).</t>
+    <t xml:space="preserve">Kilde: Hjertnes kap. 6.6 om produktutvikling, 6.7 om livssyklusen og 6.8 om produktsanering. Dekningsbidrag per montørtime: Økonomistyring for LØM-emnet kap. 2. Markedstall: NVE, «Solkraft», nve.no/energi/energisystem/solkraft (tall per 31.12.2024, hentet 09.09.2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Din egen bedrift</t>
